--- a/output/Tables/7000 steps/cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/cases_prev_7000steps.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -485,7 +485,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -494,22 +494,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>3629.613692065931</v>
+        <v>10676.70647867835</v>
       </c>
       <c r="D6">
-        <v>276.4774555870436</v>
+        <v>656.5097886851622</v>
       </c>
       <c r="E6">
-        <v>4578.371663237075</v>
+        <v>-110.1153824553654</v>
       </c>
       <c r="F6">
-        <v>1987.566796274164</v>
+        <v>21767.73203914123</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -518,22 +518,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>12750.78908252082</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>812.0306083441208</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>-131.5066607135276</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>25996.3838652124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>10676.70647867835</v>
+        <v>14609.69221040514</v>
       </c>
       <c r="D8">
-        <v>656.5097886851622</v>
+        <v>883.2828775745671</v>
       </c>
       <c r="E8">
-        <v>-110.1153824553654</v>
+        <v>-232.3548881812114</v>
       </c>
       <c r="F8">
-        <v>21767.73203914123</v>
+        <v>27299.79210828945</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -566,22 +566,22 @@
         </is>
       </c>
       <c r="C9">
-        <v>12750.78908252082</v>
+        <v>16823.58541287801</v>
       </c>
       <c r="D9">
-        <v>812.0306083441208</v>
+        <v>1041.841811288914</v>
       </c>
       <c r="E9">
-        <v>-131.5066607135276</v>
+        <v>-267.5650007624584</v>
       </c>
       <c r="F9">
-        <v>25996.3838652124</v>
+        <v>31436.69131924065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -590,22 +590,22 @@
         </is>
       </c>
       <c r="C10">
-        <v>14609.69221040514</v>
+        <v>11295.22216359617</v>
       </c>
       <c r="D10">
-        <v>883.2828775745671</v>
+        <v>1272.159851681472</v>
       </c>
       <c r="E10">
-        <v>-232.3548881812114</v>
+        <v>8177.773310166796</v>
       </c>
       <c r="F10">
-        <v>27299.79210828945</v>
+        <v>14005.53935045447</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="C11">
-        <v>16823.58541287801</v>
+        <v>6108.10108827936</v>
       </c>
       <c r="D11">
-        <v>1041.841811288914</v>
+        <v>571.3012458570594</v>
       </c>
       <c r="E11">
-        <v>-267.5650007624584</v>
+        <v>4422.282743275283</v>
       </c>
       <c r="F11">
-        <v>31436.69131924065</v>
+        <v>7573.755425914868</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>11295.22216359617</v>
+        <v>627401.4401708276</v>
       </c>
       <c r="D12">
-        <v>1272.159851681472</v>
+        <v>35468.71647922999</v>
       </c>
       <c r="E12">
-        <v>8177.773310166796</v>
+        <v>461939.5259119386</v>
       </c>
       <c r="F12">
-        <v>14005.53935045447</v>
+        <v>755869.0542637333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -662,63 +662,15 @@
         </is>
       </c>
       <c r="C13">
-        <v>6108.10108827936</v>
+        <v>277727.4893059632</v>
       </c>
       <c r="D13">
-        <v>571.3012458570594</v>
+        <v>16149.36229350632</v>
       </c>
       <c r="E13">
-        <v>4422.282743275283</v>
+        <v>204483.5993806107</v>
       </c>
       <c r="F13">
-        <v>7573.755425914868</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>627401.4401708276</v>
-      </c>
-      <c r="D14">
-        <v>35468.71647922999</v>
-      </c>
-      <c r="E14">
-        <v>461939.5259119386</v>
-      </c>
-      <c r="F14">
-        <v>755869.0542637333</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>277727.4893059632</v>
-      </c>
-      <c r="D15">
-        <v>16149.36229350632</v>
-      </c>
-      <c r="E15">
-        <v>204483.5993806107</v>
-      </c>
-      <c r="F15">
         <v>334595.3662898528</v>
       </c>
     </row>

--- a/output/Tables/7000 steps/cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/cases_prev_7000steps.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,22 +367,62 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases</t>
+          <t>tot_cases_mid</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_se</t>
+          <t>tot_cases_low</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_low</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_up</t>
+          <t>tot_daly_mid</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
@@ -401,13 +441,37 @@
         <v>66398.76344547827</v>
       </c>
       <c r="D2">
-        <v>6115.251494207865</v>
+        <v>57325.170730447</v>
       </c>
       <c r="E2">
-        <v>57325.170730447</v>
+        <v>75035.38575438136</v>
       </c>
       <c r="F2">
-        <v>75035.38575438136</v>
+        <v>118882.4624498344</v>
+      </c>
+      <c r="G2">
+        <v>102636.8128434906</v>
+      </c>
+      <c r="H2">
+        <v>134345.746313166</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>15811367505.82797</v>
+      </c>
+      <c r="M2">
+        <v>13650696108.18425</v>
+      </c>
+      <c r="N2">
+        <v>17867984259.65108</v>
       </c>
     </row>
     <row r="3">
@@ -425,19 +489,43 @@
         <v>101339.8996129359</v>
       </c>
       <c r="D3">
-        <v>7426.082993779324</v>
+        <v>87491.4945048355</v>
       </c>
       <c r="E3">
-        <v>87491.4945048355</v>
+        <v>114521.3866220694</v>
       </c>
       <c r="F3">
-        <v>114521.3866220694</v>
+        <v>155095.9907746791</v>
+      </c>
+      <c r="G3">
+        <v>133901.6525219916</v>
+      </c>
+      <c r="H3">
+        <v>175269.6419759695</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>20627766773.03232</v>
+      </c>
+      <c r="M3">
+        <v>17808919785.42489</v>
+      </c>
+      <c r="N3">
+        <v>23310862382.80394</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -446,22 +534,46 @@
         </is>
       </c>
       <c r="C4">
-        <v>21087.17857458489</v>
+        <v>3575.27802381218</v>
       </c>
       <c r="D4">
-        <v>1575.26491287042</v>
+        <v>-36.87402175591831</v>
       </c>
       <c r="E4">
-        <v>12932.80264864024</v>
+        <v>7289.297888182457</v>
       </c>
       <c r="F4">
-        <v>28548.6070925464</v>
+        <v>975.3694705317358</v>
+      </c>
+      <c r="G4">
+        <v>-7.565501948791065</v>
+      </c>
+      <c r="H4">
+        <v>2515.90166751479</v>
+      </c>
+      <c r="I4">
+        <v>157623282.2358067</v>
+      </c>
+      <c r="J4">
+        <v>-1625664.997153174</v>
+      </c>
+      <c r="K4">
+        <v>321363275.9962993</v>
+      </c>
+      <c r="L4">
+        <v>129724139.5807209</v>
+      </c>
+      <c r="M4">
+        <v>-1006211.759189212</v>
+      </c>
+      <c r="N4">
+        <v>334614921.779467</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -470,22 +582,46 @@
         </is>
       </c>
       <c r="C5">
-        <v>32689.22736066739</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>2078.28541757923</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>20048.35899201673</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>44255.89249779395</v>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -494,22 +630,46 @@
         </is>
       </c>
       <c r="C6">
-        <v>10676.70647867835</v>
+        <v>21087.17857458489</v>
       </c>
       <c r="D6">
-        <v>656.5097886851622</v>
+        <v>12932.80264864024</v>
       </c>
       <c r="E6">
-        <v>-110.1153824553654</v>
+        <v>28548.6070925464</v>
       </c>
       <c r="F6">
-        <v>21767.73203914123</v>
+        <v>3438.876348739352</v>
+      </c>
+      <c r="G6">
+        <v>1655.333554531869</v>
+      </c>
+      <c r="H6">
+        <v>5675.22734654423</v>
+      </c>
+      <c r="I6">
+        <v>1174598020.96153</v>
+      </c>
+      <c r="J6">
+        <v>720382973.1345592</v>
+      </c>
+      <c r="K6">
+        <v>1590214512.269022</v>
+      </c>
+      <c r="L6">
+        <v>457370554.3823338</v>
+      </c>
+      <c r="M6">
+        <v>220159362.7527386</v>
+      </c>
+      <c r="N6">
+        <v>754805237.0903827</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -518,22 +678,46 @@
         </is>
       </c>
       <c r="C7">
-        <v>12750.78908252082</v>
+        <v>32689.22736066739</v>
       </c>
       <c r="D7">
-        <v>812.0306083441208</v>
+        <v>20048.35899201673</v>
       </c>
       <c r="E7">
-        <v>-131.5066607135276</v>
+        <v>44255.89249779395</v>
       </c>
       <c r="F7">
-        <v>25996.3838652124</v>
+        <v>4815.458054813043</v>
+      </c>
+      <c r="G7">
+        <v>2317.963337499747</v>
+      </c>
+      <c r="H7">
+        <v>7947.02003427077</v>
+      </c>
+      <c r="I7">
+        <v>1820855342.443885</v>
+      </c>
+      <c r="J7">
+        <v>1116733692.573322</v>
+      </c>
+      <c r="K7">
+        <v>2465141723.912116</v>
+      </c>
+      <c r="L7">
+        <v>640455921.2901347</v>
+      </c>
+      <c r="M7">
+        <v>308289123.8874664</v>
+      </c>
+      <c r="N7">
+        <v>1056953664.558012</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -542,22 +726,46 @@
         </is>
       </c>
       <c r="C8">
-        <v>14609.69221040514</v>
+        <v>10676.70647867835</v>
       </c>
       <c r="D8">
-        <v>883.2828775745671</v>
+        <v>-110.1153824553654</v>
       </c>
       <c r="E8">
-        <v>-232.3548881812114</v>
+        <v>21767.73203914123</v>
       </c>
       <c r="F8">
-        <v>27299.79210828945</v>
+        <v>2078.822191287258</v>
+      </c>
+      <c r="G8">
+        <v>-16.96254972868347</v>
+      </c>
+      <c r="H8">
+        <v>4894.022491592526</v>
+      </c>
+      <c r="I8">
+        <v>158089992.8297897</v>
+      </c>
+      <c r="J8">
+        <v>-1630478.468016595</v>
+      </c>
+      <c r="K8">
+        <v>322314808.3035654</v>
+      </c>
+      <c r="L8">
+        <v>276483351.4412053</v>
+      </c>
+      <c r="M8">
+        <v>-2256019.113914901</v>
+      </c>
+      <c r="N8">
+        <v>650904991.381806</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -566,22 +774,46 @@
         </is>
       </c>
       <c r="C9">
-        <v>16823.58541287801</v>
+        <v>12750.78908252082</v>
       </c>
       <c r="D9">
-        <v>1041.841811288914</v>
+        <v>-131.5066607135276</v>
       </c>
       <c r="E9">
-        <v>-267.5650007624584</v>
+        <v>25996.3838652124</v>
       </c>
       <c r="F9">
-        <v>31436.69131924065</v>
+        <v>1907.968223277289</v>
+      </c>
+      <c r="G9">
+        <v>-15.56843389671931</v>
+      </c>
+      <c r="H9">
+        <v>4491.793207278004</v>
+      </c>
+      <c r="I9">
+        <v>188800933.9448861</v>
+      </c>
+      <c r="J9">
+        <v>-1947219.125185205</v>
+      </c>
+      <c r="K9">
+        <v>384928455.8921987</v>
+      </c>
+      <c r="L9">
+        <v>253759773.6958795</v>
+      </c>
+      <c r="M9">
+        <v>-2070601.708263668</v>
+      </c>
+      <c r="N9">
+        <v>597408496.5679746</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -590,22 +822,46 @@
         </is>
       </c>
       <c r="C10">
-        <v>11295.22216359617</v>
+        <v>14609.69221040514</v>
       </c>
       <c r="D10">
-        <v>1272.159851681472</v>
+        <v>-232.3548881812114</v>
       </c>
       <c r="E10">
-        <v>8177.773310166796</v>
+        <v>27299.79210828945</v>
       </c>
       <c r="F10">
-        <v>14005.53935045447</v>
+        <v>4003.701699700935</v>
+      </c>
+      <c r="G10">
+        <v>-47.3866520456784</v>
+      </c>
+      <c r="H10">
+        <v>9498.442412923026</v>
+      </c>
+      <c r="I10">
+        <v>1098663463.914679</v>
+      </c>
+      <c r="J10">
+        <v>-17473319.9461153</v>
+      </c>
+      <c r="K10">
+        <v>2052971666.335473</v>
+      </c>
+      <c r="L10">
+        <v>532492326.0602244</v>
+      </c>
+      <c r="M10">
+        <v>-6302424.722075228</v>
+      </c>
+      <c r="N10">
+        <v>1263292840.918762</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,22 +870,46 @@
         </is>
       </c>
       <c r="C11">
-        <v>6108.10108827936</v>
+        <v>16823.58541287801</v>
       </c>
       <c r="D11">
-        <v>571.3012458570594</v>
+        <v>-267.5650007624584</v>
       </c>
       <c r="E11">
-        <v>4422.282743275283</v>
+        <v>31436.69131924065</v>
       </c>
       <c r="F11">
-        <v>7573.755425914868</v>
+        <v>3646.244714025668</v>
+      </c>
+      <c r="G11">
+        <v>-43.15589484347326</v>
+      </c>
+      <c r="H11">
+        <v>8650.406058519478</v>
+      </c>
+      <c r="I11">
+        <v>1265150446.633837</v>
+      </c>
+      <c r="J11">
+        <v>-20121155.62233757</v>
+      </c>
+      <c r="K11">
+        <v>2364070623.898221</v>
+      </c>
+      <c r="L11">
+        <v>484950546.9654139</v>
+      </c>
+      <c r="M11">
+        <v>-5739734.014181944</v>
+      </c>
+      <c r="N11">
+        <v>1150504005.783091</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -638,40 +918,184 @@
         </is>
       </c>
       <c r="C12">
-        <v>627401.4401708276</v>
+        <v>11295.22216359617</v>
       </c>
       <c r="D12">
-        <v>35468.71647922999</v>
+        <v>8177.773310166796</v>
       </c>
       <c r="E12">
-        <v>461939.5259119386</v>
+        <v>14005.53935045447</v>
       </c>
       <c r="F12">
-        <v>755869.0542637333</v>
+        <v>2815.738768641944</v>
+      </c>
+      <c r="G12">
+        <v>1634.767903873348</v>
+      </c>
+      <c r="H12">
+        <v>3976.311883475833</v>
+      </c>
+      <c r="I12">
+        <v>190200246.0127967</v>
+      </c>
+      <c r="J12">
+        <v>137705524.7698984</v>
+      </c>
+      <c r="K12">
+        <v>235839277.1223028</v>
+      </c>
+      <c r="L12">
+        <v>374493256.2293786</v>
+      </c>
+      <c r="M12">
+        <v>217424131.2151553</v>
+      </c>
+      <c r="N12">
+        <v>528849480.5022858</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>6108.10108827936</v>
+      </c>
+      <c r="D13">
+        <v>4422.282743275283</v>
+      </c>
+      <c r="E13">
+        <v>7573.755425914868</v>
+      </c>
+      <c r="F13">
+        <v>895.7120796130496</v>
+      </c>
+      <c r="G13">
+        <v>520.0345199527512</v>
+      </c>
+      <c r="H13">
+        <v>1264.900929732205</v>
+      </c>
+      <c r="I13">
+        <v>102854314.2255365</v>
+      </c>
+      <c r="J13">
+        <v>74466819.11401233</v>
+      </c>
+      <c r="K13">
+        <v>127534467.6169806</v>
+      </c>
+      <c r="L13">
+        <v>119129706.5885356</v>
+      </c>
+      <c r="M13">
+        <v>69164591.15371591</v>
+      </c>
+      <c r="N13">
+        <v>168231823.6543833</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>dep</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>627401.4401708276</v>
+      </c>
+      <c r="D14">
+        <v>461939.5259119386</v>
+      </c>
+      <c r="E14">
+        <v>755869.0542637333</v>
+      </c>
+      <c r="F14">
+        <v>720277.1109552021</v>
+      </c>
+      <c r="G14">
+        <v>328055.8565353889</v>
+      </c>
+      <c r="H14">
+        <v>1326000.369545894</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>95796855757.04189</v>
+      </c>
+      <c r="M14">
+        <v>43631428919.20672</v>
+      </c>
+      <c r="N14">
+        <v>176358049149.6039</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C15">
         <v>277727.4893059632</v>
       </c>
-      <c r="D13">
-        <v>16149.36229350632</v>
-      </c>
-      <c r="E13">
+      <c r="D15">
         <v>204483.5993806107</v>
       </c>
-      <c r="F13">
+      <c r="E15">
         <v>334595.3662898528</v>
+      </c>
+      <c r="F15">
+        <v>285767.8531211635</v>
+      </c>
+      <c r="G15">
+        <v>130155.2088773413</v>
+      </c>
+      <c r="H15">
+        <v>526086.7978165785</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>38007124465.11475</v>
+      </c>
+      <c r="M15">
+        <v>17310642780.68639</v>
+      </c>
+      <c r="N15">
+        <v>69969544109.60495</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/cases_prev_7000steps.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>66398.76344547827</v>
+        <v>68586.37060359692</v>
       </c>
       <c r="D2">
-        <v>57325.170730447</v>
+        <v>58710.64390858215</v>
       </c>
       <c r="E2">
-        <v>75035.38575438136</v>
+        <v>77619.82193126234</v>
       </c>
       <c r="F2">
-        <v>118882.4624498344</v>
+        <v>122799.2240329562</v>
       </c>
       <c r="G2">
-        <v>102636.8128434906</v>
+        <v>105117.4081818382</v>
       </c>
       <c r="H2">
-        <v>134345.746313166</v>
+        <v>138973.0032199053</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>15811367505.82797</v>
+        <v>16332296796.38318</v>
       </c>
       <c r="M2">
-        <v>13650696108.18425</v>
+        <v>13980615288.18448</v>
       </c>
       <c r="N2">
-        <v>17867984259.65108</v>
+        <v>18483409428.2474</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>101339.8996129359</v>
+        <v>104678.695070751</v>
       </c>
       <c r="D3">
-        <v>87491.4945048355</v>
+        <v>89606.04763057169</v>
       </c>
       <c r="E3">
-        <v>114521.3866220694</v>
+        <v>118465.835119762</v>
       </c>
       <c r="F3">
-        <v>155095.9907746791</v>
+        <v>160205.8615314264</v>
       </c>
       <c r="G3">
-        <v>133901.6525219916</v>
+        <v>137137.8774771607</v>
       </c>
       <c r="H3">
-        <v>175269.6419759695</v>
+        <v>181306.4364680289</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>20627766773.03232</v>
+        <v>21307379583.67971</v>
       </c>
       <c r="M3">
-        <v>17808919785.42489</v>
+        <v>18239337704.46237</v>
       </c>
       <c r="N3">
-        <v>23310862382.80394</v>
+        <v>24113756050.24784</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>3575.27802381218</v>
+        <v>5267.734272269137</v>
       </c>
       <c r="D4">
-        <v>-36.87402175591831</v>
+        <v>-109.9778120386587</v>
       </c>
       <c r="E4">
-        <v>7289.297888182457</v>
+        <v>10508.09459977117</v>
       </c>
       <c r="F4">
-        <v>975.3694705317358</v>
+        <v>1425.104132033504</v>
       </c>
       <c r="G4">
-        <v>-7.565501948791065</v>
+        <v>-22.37616814995075</v>
       </c>
       <c r="H4">
-        <v>2515.90166751479</v>
+        <v>3596.626500588687</v>
       </c>
       <c r="I4">
-        <v>157623282.2358067</v>
+        <v>232238600.8615297</v>
       </c>
       <c r="J4">
-        <v>-1625664.997153174</v>
+        <v>-4848591.799348344</v>
       </c>
       <c r="K4">
-        <v>321363275.9962993</v>
+        <v>463270366.6201096</v>
       </c>
       <c r="L4">
-        <v>129724139.5807209</v>
+        <v>189538849.5604561</v>
       </c>
       <c r="M4">
-        <v>-1006211.759189212</v>
+        <v>-2976030.36394345</v>
       </c>
       <c r="N4">
-        <v>334614921.779467</v>
+        <v>478351324.5782954</v>
       </c>
     </row>
     <row r="5">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>21087.17857458489</v>
+        <v>67272.25267452786</v>
       </c>
       <c r="D6">
-        <v>12932.80264864024</v>
+        <v>43957.41469438181</v>
       </c>
       <c r="E6">
-        <v>28548.6070925464</v>
+        <v>88207.3628523323</v>
       </c>
       <c r="F6">
-        <v>3438.876348739352</v>
+        <v>10441.48314496201</v>
       </c>
       <c r="G6">
-        <v>1655.333554531869</v>
+        <v>5354.921969340434</v>
       </c>
       <c r="H6">
-        <v>5675.22734654423</v>
+        <v>16689.03844293452</v>
       </c>
       <c r="I6">
-        <v>1174598020.96153</v>
+        <v>3747199018.476547</v>
       </c>
       <c r="J6">
-        <v>720382973.1345592</v>
+        <v>2448515913.30646</v>
       </c>
       <c r="K6">
-        <v>1590214512.269022</v>
+        <v>4913326525.600606</v>
       </c>
       <c r="L6">
-        <v>457370554.3823338</v>
+        <v>1388717258.279947</v>
       </c>
       <c r="M6">
-        <v>220159362.7527386</v>
+        <v>712204621.9222777</v>
       </c>
       <c r="N6">
-        <v>754805237.0903827</v>
+        <v>2219642112.910292</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>32689.22736066739</v>
+        <v>86461.39193134329</v>
       </c>
       <c r="D7">
-        <v>20048.35899201673</v>
+        <v>56496.09027614217</v>
       </c>
       <c r="E7">
-        <v>44255.89249779395</v>
+        <v>113368.1580086796</v>
       </c>
       <c r="F7">
-        <v>4815.458054813043</v>
+        <v>10992.80153703313</v>
       </c>
       <c r="G7">
-        <v>2317.963337499747</v>
+        <v>5637.665994189798</v>
       </c>
       <c r="H7">
-        <v>7947.02003427077</v>
+        <v>17570.23259053153</v>
       </c>
       <c r="I7">
-        <v>1820855342.443885</v>
+        <v>4816072453.3597</v>
       </c>
       <c r="J7">
-        <v>1116733692.573322</v>
+        <v>3146945220.56166</v>
       </c>
       <c r="K7">
-        <v>2465141723.912116</v>
+        <v>6314833137.399492</v>
       </c>
       <c r="L7">
-        <v>640455921.2901347</v>
+        <v>1462042604.425406</v>
       </c>
       <c r="M7">
-        <v>308289123.8874664</v>
+        <v>749809577.2272431</v>
       </c>
       <c r="N7">
-        <v>1056953664.558012</v>
+        <v>2336840934.540693</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>10676.70647867835</v>
+        <v>80903.92992485018</v>
       </c>
       <c r="D8">
-        <v>-110.1153824553654</v>
+        <v>-1689.082390754535</v>
       </c>
       <c r="E8">
-        <v>21767.73203914123</v>
+        <v>161387.440064886</v>
       </c>
       <c r="F8">
-        <v>2078.822191287258</v>
+        <v>23543.62622491</v>
       </c>
       <c r="G8">
-        <v>-16.96254972868347</v>
+        <v>-388.8818481542627</v>
       </c>
       <c r="H8">
-        <v>4894.022491592526</v>
+        <v>54230.82440651565</v>
       </c>
       <c r="I8">
-        <v>158089992.8297897</v>
+        <v>1197944490.39726</v>
       </c>
       <c r="J8">
-        <v>-1630478.468016595</v>
+        <v>-25010242.95990245</v>
       </c>
       <c r="K8">
-        <v>322314808.3035654</v>
+        <v>2389663825.040776</v>
       </c>
       <c r="L8">
-        <v>276483351.4412053</v>
+        <v>3131302287.913031</v>
       </c>
       <c r="M8">
-        <v>-2256019.113914901</v>
+        <v>-51721285.80451694</v>
       </c>
       <c r="N8">
-        <v>650904991.381806</v>
+        <v>7212699646.066581</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>12750.78908252082</v>
+        <v>51212.84679198766</v>
       </c>
       <c r="D9">
-        <v>-131.5066607135276</v>
+        <v>-1069.202914828812</v>
       </c>
       <c r="E9">
-        <v>25996.3838652124</v>
+        <v>102159.5644348961</v>
       </c>
       <c r="F9">
-        <v>1907.968223277289</v>
+        <v>8420.880817681866</v>
       </c>
       <c r="G9">
-        <v>-15.56843389671931</v>
+        <v>-139.0918996157926</v>
       </c>
       <c r="H9">
-        <v>4491.793207278004</v>
+        <v>19396.812734341</v>
       </c>
       <c r="I9">
-        <v>188800933.9448861</v>
+        <v>758308622.4489565</v>
       </c>
       <c r="J9">
-        <v>-1947219.125185205</v>
+        <v>-15831687.55987027</v>
       </c>
       <c r="K9">
-        <v>384928455.8921987</v>
+        <v>1512676670.587509</v>
       </c>
       <c r="L9">
-        <v>253759773.6958795</v>
+        <v>1119977148.751688</v>
       </c>
       <c r="M9">
-        <v>-2070601.708263668</v>
+        <v>-18499222.64890042</v>
       </c>
       <c r="N9">
-        <v>597408496.5679746</v>
+        <v>2579776093.667353</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>14609.69221040514</v>
+        <v>12335.51081750371</v>
       </c>
       <c r="D10">
-        <v>-232.3548881812114</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>27299.79210828945</v>
+        <v>22493.13134572677</v>
       </c>
       <c r="F10">
-        <v>4003.701699700935</v>
+        <v>4275.978687774265</v>
       </c>
       <c r="G10">
-        <v>-47.3866520456784</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>9498.442412923026</v>
+        <v>9899.21418616458</v>
       </c>
       <c r="I10">
-        <v>1098663463.914679</v>
+        <v>927642748.9870987</v>
       </c>
       <c r="J10">
-        <v>-17473319.9461153</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>2052971666.335473</v>
+        <v>1691505970.330006</v>
       </c>
       <c r="L10">
-        <v>532492326.0602244</v>
+        <v>568705165.4739773</v>
       </c>
       <c r="M10">
-        <v>-6302424.722075228</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>1263292840.918762</v>
+        <v>1316595486.759889</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>16823.58541287801</v>
+        <v>16341.50219780824</v>
       </c>
       <c r="D11">
-        <v>-267.5650007624584</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>31436.69131924065</v>
+        <v>29797.83818925521</v>
       </c>
       <c r="F11">
-        <v>3646.244714025668</v>
+        <v>4996.956599485138</v>
       </c>
       <c r="G11">
-        <v>-43.15589484347326</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>8650.406058519478</v>
+        <v>11568.33260154067</v>
       </c>
       <c r="I11">
-        <v>1265150446.633837</v>
+        <v>1228897306.777378</v>
       </c>
       <c r="J11">
-        <v>-20121155.62233757</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>2364070623.898221</v>
+        <v>2240827229.670175</v>
       </c>
       <c r="L11">
-        <v>484950546.9654139</v>
+        <v>664595227.7315234</v>
       </c>
       <c r="M11">
-        <v>-5739734.014181944</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>1150504005.783091</v>
+        <v>1538588236.004909</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>11295.22216359617</v>
+        <v>32171.39524575697</v>
       </c>
       <c r="D12">
-        <v>8177.773310166796</v>
+        <v>23811.65577163275</v>
       </c>
       <c r="E12">
-        <v>14005.53935045447</v>
+        <v>39090.87851330139</v>
       </c>
       <c r="F12">
-        <v>2815.738768641944</v>
+        <v>8964.67197227111</v>
       </c>
       <c r="G12">
-        <v>1634.767903873348</v>
+        <v>5320.807584618855</v>
       </c>
       <c r="H12">
-        <v>3976.311883475833</v>
+        <v>12405.74806267202</v>
       </c>
       <c r="I12">
-        <v>190200246.0127967</v>
+        <v>541734124.5433004</v>
       </c>
       <c r="J12">
-        <v>137705524.7698984</v>
+        <v>400964471.538523</v>
       </c>
       <c r="K12">
-        <v>235839277.1223028</v>
+        <v>658251303.2854826</v>
       </c>
       <c r="L12">
-        <v>374493256.2293786</v>
+        <v>1192301372.312057</v>
       </c>
       <c r="M12">
-        <v>217424131.2151553</v>
+        <v>707667408.7543077</v>
       </c>
       <c r="N12">
-        <v>528849480.5022858</v>
+        <v>1649964492.335379</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>6108.10108827936</v>
+        <v>22607.42410015239</v>
       </c>
       <c r="D13">
-        <v>4422.282743275283</v>
+        <v>16732.88324749115</v>
       </c>
       <c r="E13">
-        <v>7573.755425914868</v>
+        <v>27469.8707422177</v>
       </c>
       <c r="F13">
-        <v>895.7120796130496</v>
+        <v>3724.500821296638</v>
       </c>
       <c r="G13">
-        <v>520.0345199527512</v>
+        <v>2210.605394170793</v>
       </c>
       <c r="H13">
-        <v>1264.900929732205</v>
+        <v>5154.144958247179</v>
       </c>
       <c r="I13">
-        <v>102854314.2255365</v>
+        <v>380686414.422466</v>
       </c>
       <c r="J13">
-        <v>74466819.11401233</v>
+        <v>281765021.0045031</v>
       </c>
       <c r="K13">
-        <v>127534467.6169806</v>
+        <v>462565153.4282026</v>
       </c>
       <c r="L13">
-        <v>119129706.5885356</v>
+        <v>495358609.2324529</v>
       </c>
       <c r="M13">
-        <v>69164591.15371591</v>
+        <v>294010517.4247155</v>
       </c>
       <c r="N13">
-        <v>168231823.6543833</v>
+        <v>685501279.4468747</v>
       </c>
     </row>
     <row r="14">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C14">
-        <v>627401.4401708276</v>
+        <v>424800.9076185662</v>
       </c>
       <c r="D14">
-        <v>461939.5259119386</v>
+        <v>319020.455855674</v>
       </c>
       <c r="E14">
-        <v>755869.0542637333</v>
+        <v>508614.5913819045</v>
       </c>
       <c r="F14">
-        <v>720277.1109552021</v>
+        <v>410810.763891281</v>
       </c>
       <c r="G14">
-        <v>328055.8565353889</v>
+        <v>190846.1828195405</v>
       </c>
       <c r="H14">
-        <v>1326000.369545894</v>
+        <v>751602.4213941777</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>95796855757.04189</v>
+        <v>54637831597.54037</v>
       </c>
       <c r="M14">
-        <v>43631428919.20672</v>
+        <v>25382542314.99888</v>
       </c>
       <c r="N14">
-        <v>176358049149.6039</v>
+        <v>99963122045.42563</v>
       </c>
     </row>
     <row r="15">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="C15">
-        <v>277727.4893059632</v>
+        <v>209223.0341274764</v>
       </c>
       <c r="D15">
-        <v>204483.5993806107</v>
+        <v>157124.0233384507</v>
       </c>
       <c r="E15">
-        <v>334595.3662898528</v>
+        <v>250502.9676301416</v>
       </c>
       <c r="F15">
-        <v>285767.8531211635</v>
+        <v>172994.9280803206</v>
       </c>
       <c r="G15">
-        <v>130155.2088773413</v>
+        <v>80366.49614177944</v>
       </c>
       <c r="H15">
-        <v>526086.7978165785</v>
+        <v>316504.3817315627</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1089,13 +1089,13 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>38007124465.11475</v>
+        <v>23008325434.68265</v>
       </c>
       <c r="M15">
-        <v>17310642780.68639</v>
+        <v>10688743986.85666</v>
       </c>
       <c r="N15">
-        <v>69969544109.60495</v>
+        <v>42095082770.29784</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/cases_prev_7000steps.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>68586.37060359692</v>
+        <v>60812.32702070134</v>
       </c>
       <c r="D2">
-        <v>58710.64390858215</v>
+        <v>52055.98204925901</v>
       </c>
       <c r="E2">
-        <v>77619.82193126234</v>
+        <v>68821.86581724428</v>
       </c>
       <c r="F2">
-        <v>122799.2240329562</v>
+        <v>118382.8271450311</v>
       </c>
       <c r="G2">
-        <v>105117.4081818382</v>
+        <v>101336.9266843623</v>
       </c>
       <c r="H2">
-        <v>138973.0032199053</v>
+        <v>133974.9265320482</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>16332296796.38318</v>
+        <v>15744916010.28914</v>
       </c>
       <c r="M2">
-        <v>13980615288.18448</v>
+        <v>13477811249.02019</v>
       </c>
       <c r="N2">
-        <v>18483409428.2474</v>
+        <v>17818665228.76241</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>104678.695070751</v>
+        <v>98411.13626092802</v>
       </c>
       <c r="D3">
-        <v>89606.04763057169</v>
+        <v>84240.95234675247</v>
       </c>
       <c r="E3">
-        <v>118465.835119762</v>
+        <v>111372.7815803948</v>
       </c>
       <c r="F3">
-        <v>160205.8615314264</v>
+        <v>157474.8301374887</v>
       </c>
       <c r="G3">
-        <v>137137.8774771607</v>
+        <v>134800.0863058035</v>
       </c>
       <c r="H3">
-        <v>181306.4364680289</v>
+        <v>178215.7033001934</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>21307379583.67971</v>
+        <v>20944152408.28599</v>
       </c>
       <c r="M3">
-        <v>18239337704.46237</v>
+        <v>17928411478.67187</v>
       </c>
       <c r="N3">
-        <v>24113756050.24784</v>
+        <v>23702688538.92572</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>5267.734272269137</v>
+        <v>5035.901031603633</v>
       </c>
       <c r="D4">
-        <v>-109.9778120386587</v>
+        <v>-105.1376831998813</v>
       </c>
       <c r="E4">
-        <v>10508.09459977117</v>
+        <v>10045.63284707618</v>
       </c>
       <c r="F4">
-        <v>1425.104132033504</v>
+        <v>1395.252455158787</v>
       </c>
       <c r="G4">
-        <v>-22.37616814995075</v>
+        <v>-21.90745423193439</v>
       </c>
       <c r="H4">
-        <v>3596.626500588687</v>
+        <v>3521.287913238277</v>
       </c>
       <c r="I4">
-        <v>232238600.8615297</v>
+        <v>222017768.780308</v>
       </c>
       <c r="J4">
-        <v>-4848591.799348344</v>
+        <v>-4635205.039233164</v>
       </c>
       <c r="K4">
-        <v>463270366.6201096</v>
+        <v>442881815.3290466</v>
       </c>
       <c r="L4">
-        <v>189538849.5604561</v>
+        <v>185568576.5361187</v>
       </c>
       <c r="M4">
-        <v>-2976030.36394345</v>
+        <v>-2913691.412847274</v>
       </c>
       <c r="N4">
-        <v>478351324.5782954</v>
+        <v>468331292.4606909</v>
       </c>
     </row>
     <row r="5">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>67272.25267452786</v>
+        <v>62026.80069934682</v>
       </c>
       <c r="D6">
-        <v>43957.41469438181</v>
+        <v>40529.90188537803</v>
       </c>
       <c r="E6">
-        <v>88207.3628523323</v>
+        <v>81329.52738073227</v>
       </c>
       <c r="F6">
-        <v>10441.48314496201</v>
+        <v>10078.8946991901</v>
       </c>
       <c r="G6">
-        <v>5354.921969340434</v>
+        <v>5168.96823009316</v>
       </c>
       <c r="H6">
-        <v>16689.03844293452</v>
+        <v>16109.49888649032</v>
       </c>
       <c r="I6">
-        <v>3747199018.476547</v>
+        <v>3455016852.555022</v>
       </c>
       <c r="J6">
-        <v>2448515913.30646</v>
+        <v>2257596594.819324</v>
       </c>
       <c r="K6">
-        <v>4913326525.600606</v>
+        <v>4530217334.161569</v>
       </c>
       <c r="L6">
-        <v>1388717258.279947</v>
+        <v>1340492994.992283</v>
       </c>
       <c r="M6">
-        <v>712204621.9222777</v>
+        <v>687472774.6023903</v>
       </c>
       <c r="N6">
-        <v>2219642112.910292</v>
+        <v>2142563351.903212</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>86461.39193134329</v>
+        <v>82750.82644288789</v>
       </c>
       <c r="D7">
-        <v>56496.09027614217</v>
+        <v>54071.51165060037</v>
       </c>
       <c r="E7">
-        <v>113368.1580086796</v>
+        <v>108502.8653595535</v>
       </c>
       <c r="F7">
-        <v>10992.80153703313</v>
+        <v>10804.30530776621</v>
       </c>
       <c r="G7">
-        <v>5637.665994189798</v>
+        <v>5540.995570531971</v>
       </c>
       <c r="H7">
-        <v>17570.23259053153</v>
+        <v>17268.95155862159</v>
       </c>
       <c r="I7">
-        <v>4816072453.3597</v>
+        <v>4609386534.52175</v>
       </c>
       <c r="J7">
-        <v>3146945220.56166</v>
+        <v>3011891341.961739</v>
       </c>
       <c r="K7">
-        <v>6314833137.399492</v>
+        <v>6043826606.257845</v>
       </c>
       <c r="L7">
-        <v>1462042604.425406</v>
+        <v>1436972605.932906</v>
       </c>
       <c r="M7">
-        <v>749809577.2272431</v>
+        <v>736952410.8807521</v>
       </c>
       <c r="N7">
-        <v>2336840934.540693</v>
+        <v>2296770557.296672</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>80903.92992485018</v>
+        <v>78495.71499848703</v>
       </c>
       <c r="D8">
-        <v>-1689.082390754535</v>
+        <v>-1638.804568292139</v>
       </c>
       <c r="E8">
-        <v>161387.440064886</v>
+        <v>156583.5245758266</v>
       </c>
       <c r="F8">
-        <v>23543.62622491</v>
+        <v>23192.49122305101</v>
       </c>
       <c r="G8">
-        <v>-388.8818481542627</v>
+        <v>-383.0819757314634</v>
       </c>
       <c r="H8">
-        <v>54230.82440651565</v>
+        <v>53422.01354420878</v>
       </c>
       <c r="I8">
-        <v>1197944490.39726</v>
+        <v>1162286051.982595</v>
       </c>
       <c r="J8">
-        <v>-25010242.95990245</v>
+        <v>-24265779.24270174</v>
       </c>
       <c r="K8">
-        <v>2389663825.040776</v>
+        <v>2318532248.394261</v>
       </c>
       <c r="L8">
-        <v>3131302287.913031</v>
+        <v>3084601332.665784</v>
       </c>
       <c r="M8">
-        <v>-51721285.80451694</v>
+        <v>-50949902.77228463</v>
       </c>
       <c r="N8">
-        <v>7212699646.066581</v>
+        <v>7105127801.379767</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>51212.84679198766</v>
+        <v>49665.12484193227</v>
       </c>
       <c r="D9">
-        <v>-1069.202914828812</v>
+        <v>-1036.890147154239</v>
       </c>
       <c r="E9">
-        <v>102159.5644348961</v>
+        <v>99072.16331997342</v>
       </c>
       <c r="F9">
-        <v>8420.880817681866</v>
+        <v>8301.648432193135</v>
       </c>
       <c r="G9">
-        <v>-139.0918996157926</v>
+        <v>-137.1224786784323</v>
       </c>
       <c r="H9">
-        <v>19396.812734341</v>
+        <v>19122.17065077916</v>
       </c>
       <c r="I9">
-        <v>758308622.4489565</v>
+        <v>735391503.5344914</v>
       </c>
       <c r="J9">
-        <v>-15831687.55987027</v>
+        <v>-15353232.40891281</v>
       </c>
       <c r="K9">
-        <v>1512676670.587509</v>
+        <v>1466961522.278845</v>
       </c>
       <c r="L9">
-        <v>1119977148.751688</v>
+        <v>1104119241.481687</v>
       </c>
       <c r="M9">
-        <v>-18499222.64890042</v>
+        <v>-18237289.6642315</v>
       </c>
       <c r="N9">
-        <v>2579776093.667353</v>
+        <v>2543248696.553628</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>12335.51081750371</v>
+        <v>12056.6702807696</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>22493.13134572677</v>
+        <v>21984.68083159204</v>
       </c>
       <c r="F10">
-        <v>4275.978687774265</v>
+        <v>4204.416841200173</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>9899.21418616458</v>
+        <v>9733.543096919055</v>
       </c>
       <c r="I10">
-        <v>927642748.9870987</v>
+        <v>906673661.7841525</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1691505970.330006</v>
+        <v>1653269983.216557</v>
       </c>
       <c r="L10">
-        <v>568705165.4739773</v>
+        <v>559187439.8796229</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10">
-        <v>1316595486.759889</v>
+        <v>1294561231.890234</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>16341.50219780824</v>
+        <v>16096.82026023769</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>29797.83818925521</v>
+        <v>29351.67401809747</v>
       </c>
       <c r="F11">
-        <v>4996.956599485138</v>
+        <v>4938.096070794879</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>11568.33260154067</v>
+        <v>11432.06602418805</v>
       </c>
       <c r="I11">
-        <v>1228897306.777378</v>
+        <v>1210496980.390138</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>2240827229.670175</v>
+        <v>2207275237.834931</v>
       </c>
       <c r="L11">
-        <v>664595227.7315234</v>
+        <v>656766777.4157189</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <v>1538588236.004909</v>
+        <v>1520464781.217011</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>32171.39524575697</v>
+        <v>28474.64780985158</v>
       </c>
       <c r="D12">
-        <v>23811.65577163275</v>
+        <v>21075.50843496856</v>
       </c>
       <c r="E12">
-        <v>39090.87851330139</v>
+        <v>34599.02779288883</v>
       </c>
       <c r="F12">
-        <v>8964.67197227111</v>
+        <v>8475.041174562864</v>
       </c>
       <c r="G12">
-        <v>5320.807584618855</v>
+        <v>5030.196698892414</v>
       </c>
       <c r="H12">
-        <v>12405.74806267202</v>
+        <v>11728.17320673951</v>
       </c>
       <c r="I12">
-        <v>541734124.5433004</v>
+        <v>479484594.4700922</v>
       </c>
       <c r="J12">
-        <v>400964471.538523</v>
+        <v>354890486.5364367</v>
       </c>
       <c r="K12">
-        <v>658251303.2854826</v>
+        <v>582613029.0044533</v>
       </c>
       <c r="L12">
-        <v>1192301372.312057</v>
+        <v>1127180476.216861</v>
       </c>
       <c r="M12">
-        <v>707667408.7543077</v>
+        <v>669016160.9526911</v>
       </c>
       <c r="N12">
-        <v>1649964492.335379</v>
+        <v>1559847036.496355</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>22607.42410015239</v>
+        <v>20961.21919971283</v>
       </c>
       <c r="D13">
-        <v>16732.88324749115</v>
+        <v>15514.44481423692</v>
       </c>
       <c r="E13">
-        <v>27469.8707422177</v>
+        <v>25469.59704319076</v>
       </c>
       <c r="F13">
-        <v>3724.500821296638</v>
+        <v>3640.729485625794</v>
       </c>
       <c r="G13">
-        <v>2210.605394170793</v>
+        <v>2160.884538841149</v>
       </c>
       <c r="H13">
-        <v>5154.144958247179</v>
+        <v>5038.218119159203</v>
       </c>
       <c r="I13">
-        <v>380686414.422466</v>
+        <v>352965970.1039641</v>
       </c>
       <c r="J13">
-        <v>281765021.0045031</v>
+        <v>261247736.226935</v>
       </c>
       <c r="K13">
-        <v>462565153.4282026</v>
+        <v>428882544.6102901</v>
       </c>
       <c r="L13">
-        <v>495358609.2324529</v>
+        <v>484217021.5882306</v>
       </c>
       <c r="M13">
-        <v>294010517.4247155</v>
+        <v>287397643.6658728</v>
       </c>
       <c r="N13">
-        <v>685501279.4468747</v>
+        <v>670083009.848174</v>
       </c>
     </row>
     <row r="14">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="C14">
-        <v>424800.9076185662</v>
+        <v>412256.2595949728</v>
       </c>
       <c r="D14">
-        <v>319020.455855674</v>
+        <v>309599.5736041024</v>
       </c>
       <c r="E14">
-        <v>508614.5913819045</v>
+        <v>493594.8705806515</v>
       </c>
       <c r="F14">
-        <v>410810.763891281</v>
+        <v>405272.4368740573</v>
       </c>
       <c r="G14">
-        <v>190846.1828195405</v>
+        <v>188273.2985055277</v>
       </c>
       <c r="H14">
-        <v>751602.4213941777</v>
+        <v>741469.7268240846</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>54637831597.54037</v>
+        <v>53901234104.24962</v>
       </c>
       <c r="M14">
-        <v>25382542314.99888</v>
+        <v>25040348701.23519</v>
       </c>
       <c r="N14">
-        <v>99963122045.42563</v>
+        <v>98615473667.60326</v>
       </c>
     </row>
     <row r="15">
@@ -1062,22 +1062,22 @@
         </is>
       </c>
       <c r="C15">
-        <v>209223.0341274764</v>
+        <v>205076.2777874958</v>
       </c>
       <c r="D15">
-        <v>157124.0233384507</v>
+        <v>154009.8583868761</v>
       </c>
       <c r="E15">
-        <v>250502.9676301416</v>
+        <v>245538.0517281426</v>
       </c>
       <c r="F15">
-        <v>172994.9280803206</v>
+        <v>171030.3668774941</v>
       </c>
       <c r="G15">
-        <v>80366.49614177944</v>
+        <v>79453.83990336121</v>
       </c>
       <c r="H15">
-        <v>316504.3817315627</v>
+        <v>312910.1016230398</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1089,13 +1089,13 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>23008325434.68265</v>
+        <v>22747038794.70671</v>
       </c>
       <c r="M15">
-        <v>10688743986.85666</v>
+        <v>10567360707.14704</v>
       </c>
       <c r="N15">
-        <v>42095082770.29784</v>
+        <v>41617043515.86429</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/cases_prev_7000steps.xlsx
@@ -1,21 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0066AB-1925-6D42-B7C0-45CD847F934D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="33380" yWindow="-780" windowWidth="24100" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>tot_cases_mid</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly_mid</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_mid</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_mid</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +143,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +195,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +229,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +264,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,101 +440,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>sex</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_mid</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_mid</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_mid</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_mid</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>60812.32702070134</v>
+        <v>60812.327020701341</v>
       </c>
       <c r="D2">
-        <v>52055.98204925901</v>
+        <v>52055.982049259008</v>
       </c>
       <c r="E2">
-        <v>68821.86581724428</v>
+        <v>68821.865817244281</v>
       </c>
       <c r="F2">
         <v>118382.8271450311</v>
@@ -453,7 +524,7 @@
         <v>101336.9266843623</v>
       </c>
       <c r="H2">
-        <v>133974.9265320482</v>
+        <v>133974.92653204821</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,28 +536,24 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>15744916010.28914</v>
+        <v>15744916010.289141</v>
       </c>
       <c r="M2">
-        <v>13477811249.02019</v>
+        <v>13477811249.020189</v>
       </c>
       <c r="N2">
-        <v>17818665228.76241</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>17818665228.762409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>98411.13626092802</v>
+        <v>98411.136260928019</v>
       </c>
       <c r="D3">
         <v>84240.95234675247</v>
@@ -495,13 +562,13 @@
         <v>111372.7815803948</v>
       </c>
       <c r="F3">
-        <v>157474.8301374887</v>
+        <v>157474.83013748869</v>
       </c>
       <c r="G3">
         <v>134800.0863058035</v>
       </c>
       <c r="H3">
-        <v>178215.7033001934</v>
+        <v>178215.70330019339</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,73 +580,65 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>20944152408.28599</v>
+        <v>20944152408.285992</v>
       </c>
       <c r="M3">
-        <v>17928411478.67187</v>
+        <v>17928411478.671871</v>
       </c>
       <c r="N3">
         <v>23702688538.92572</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
       </c>
       <c r="C4">
-        <v>5035.901031603633</v>
+        <v>5035.9010316036329</v>
       </c>
       <c r="D4">
-        <v>-105.1376831998813</v>
+        <v>-105.13768319988129</v>
       </c>
       <c r="E4">
         <v>10045.63284707618</v>
       </c>
       <c r="F4">
-        <v>1395.252455158787</v>
+        <v>1395.2524551587869</v>
       </c>
       <c r="G4">
-        <v>-21.90745423193439</v>
+        <v>-21.907454231934391</v>
       </c>
       <c r="H4">
-        <v>3521.287913238277</v>
+        <v>3521.2879132382768</v>
       </c>
       <c r="I4">
-        <v>222017768.780308</v>
+        <v>222017768.78030801</v>
       </c>
       <c r="J4">
-        <v>-4635205.039233164</v>
+        <v>-4635205.0392331639</v>
       </c>
       <c r="K4">
-        <v>442881815.3290466</v>
+        <v>442881815.32904661</v>
       </c>
       <c r="L4">
-        <v>185568576.5361187</v>
+        <v>185568576.53611869</v>
       </c>
       <c r="M4">
         <v>-2913691.412847274</v>
       </c>
       <c r="N4">
-        <v>468331292.4606909</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>468331292.46069092</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -618,70 +677,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>62026.80069934682</v>
+        <v>62026.800699346823</v>
       </c>
       <c r="D6">
-        <v>40529.90188537803</v>
+        <v>40529.901885378029</v>
       </c>
       <c r="E6">
-        <v>81329.52738073227</v>
+        <v>81329.527380732266</v>
       </c>
       <c r="F6">
-        <v>10078.8946991901</v>
+        <v>10078.894699190099</v>
       </c>
       <c r="G6">
-        <v>5168.96823009316</v>
+        <v>5168.9682300931599</v>
       </c>
       <c r="H6">
-        <v>16109.49888649032</v>
+        <v>16109.498886490321</v>
       </c>
       <c r="I6">
-        <v>3455016852.555022</v>
+        <v>3455016852.5550218</v>
       </c>
       <c r="J6">
         <v>2257596594.819324</v>
       </c>
       <c r="K6">
-        <v>4530217334.161569</v>
+        <v>4530217334.1615686</v>
       </c>
       <c r="L6">
-        <v>1340492994.992283</v>
+        <v>1340492994.9922831</v>
       </c>
       <c r="M6">
-        <v>687472774.6023903</v>
+        <v>687472774.60239029</v>
       </c>
       <c r="N6">
-        <v>2142563351.903212</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>2142563351.9032121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
       </c>
       <c r="C7">
         <v>82750.82644288789</v>
       </c>
       <c r="D7">
-        <v>54071.51165060037</v>
+        <v>54071.511650600369</v>
       </c>
       <c r="E7">
         <v>108502.8653595535</v>
@@ -690,43 +741,39 @@
         <v>10804.30530776621</v>
       </c>
       <c r="G7">
-        <v>5540.995570531971</v>
+        <v>5540.9955705319708</v>
       </c>
       <c r="H7">
-        <v>17268.95155862159</v>
+        <v>17268.951558621589</v>
       </c>
       <c r="I7">
-        <v>4609386534.52175</v>
+        <v>4609386534.5217505</v>
       </c>
       <c r="J7">
-        <v>3011891341.961739</v>
+        <v>3011891341.9617391</v>
       </c>
       <c r="K7">
-        <v>6043826606.257845</v>
+        <v>6043826606.2578449</v>
       </c>
       <c r="L7">
-        <v>1436972605.932906</v>
+        <v>1436972605.9329059</v>
       </c>
       <c r="M7">
-        <v>736952410.8807521</v>
+        <v>736952410.88075209</v>
       </c>
       <c r="N7">
-        <v>2296770557.296672</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>2296770557.2966719</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>78495.71499848703</v>
+        <v>78495.714998487034</v>
       </c>
       <c r="D8">
         <v>-1638.804568292139</v>
@@ -735,91 +782,83 @@
         <v>156583.5245758266</v>
       </c>
       <c r="F8">
-        <v>23192.49122305101</v>
+        <v>23192.491223051009</v>
       </c>
       <c r="G8">
-        <v>-383.0819757314634</v>
+        <v>-383.08197573146339</v>
       </c>
       <c r="H8">
-        <v>53422.01354420878</v>
+        <v>53422.013544208778</v>
       </c>
       <c r="I8">
         <v>1162286051.982595</v>
       </c>
       <c r="J8">
-        <v>-24265779.24270174</v>
+        <v>-24265779.242701739</v>
       </c>
       <c r="K8">
-        <v>2318532248.394261</v>
+        <v>2318532248.3942609</v>
       </c>
       <c r="L8">
-        <v>3084601332.665784</v>
+        <v>3084601332.6657839</v>
       </c>
       <c r="M8">
-        <v>-50949902.77228463</v>
+        <v>-50949902.772284627</v>
       </c>
       <c r="N8">
-        <v>7105127801.379767</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>7105127801.3797674</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>49665.12484193227</v>
+        <v>49665.124841932273</v>
       </c>
       <c r="D9">
         <v>-1036.890147154239</v>
       </c>
       <c r="E9">
-        <v>99072.16331997342</v>
+        <v>99072.163319973421</v>
       </c>
       <c r="F9">
-        <v>8301.648432193135</v>
+        <v>8301.6484321931348</v>
       </c>
       <c r="G9">
-        <v>-137.1224786784323</v>
+        <v>-137.12247867843229</v>
       </c>
       <c r="H9">
         <v>19122.17065077916</v>
       </c>
       <c r="I9">
-        <v>735391503.5344914</v>
+        <v>735391503.53449142</v>
       </c>
       <c r="J9">
         <v>-15353232.40891281</v>
       </c>
       <c r="K9">
-        <v>1466961522.278845</v>
+        <v>1466961522.2788451</v>
       </c>
       <c r="L9">
-        <v>1104119241.481687</v>
+        <v>1104119241.4816871</v>
       </c>
       <c r="M9">
-        <v>-18237289.6642315</v>
+        <v>-18237289.664231502</v>
       </c>
       <c r="N9">
         <v>2543248696.553628</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
       </c>
       <c r="C10">
         <v>12056.6702807696</v>
@@ -828,19 +867,19 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>21984.68083159204</v>
+        <v>21984.680831592039</v>
       </c>
       <c r="F10">
-        <v>4204.416841200173</v>
+        <v>4204.4168412001727</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>9733.543096919055</v>
+        <v>9733.5430969190547</v>
       </c>
       <c r="I10">
-        <v>906673661.7841525</v>
+        <v>906673661.78415251</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -849,7 +888,7 @@
         <v>1653269983.216557</v>
       </c>
       <c r="L10">
-        <v>559187439.8796229</v>
+        <v>559187439.87962294</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -858,16 +897,12 @@
         <v>1294561231.890234</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
       </c>
       <c r="C11">
         <v>16096.82026023769</v>
@@ -879,25 +914,25 @@
         <v>29351.67401809747</v>
       </c>
       <c r="F11">
-        <v>4938.096070794879</v>
+        <v>4938.0960707948789</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>11432.06602418805</v>
+        <v>11432.066024188051</v>
       </c>
       <c r="I11">
-        <v>1210496980.390138</v>
+        <v>1210496980.3901379</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>2207275237.834931</v>
+        <v>2207275237.8349309</v>
       </c>
       <c r="L11">
-        <v>656766777.4157189</v>
+        <v>656766777.41571891</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -906,16 +941,12 @@
         <v>1520464781.217011</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
       </c>
       <c r="C12">
         <v>28474.64780985158</v>
@@ -924,22 +955,22 @@
         <v>21075.50843496856</v>
       </c>
       <c r="E12">
-        <v>34599.02779288883</v>
+        <v>34599.027792888832</v>
       </c>
       <c r="F12">
-        <v>8475.041174562864</v>
+        <v>8475.0411745628644</v>
       </c>
       <c r="G12">
-        <v>5030.196698892414</v>
+        <v>5030.1966988924141</v>
       </c>
       <c r="H12">
         <v>11728.17320673951</v>
       </c>
       <c r="I12">
-        <v>479484594.4700922</v>
+        <v>479484594.47009218</v>
       </c>
       <c r="J12">
-        <v>354890486.5364367</v>
+        <v>354890486.53643668</v>
       </c>
       <c r="K12">
         <v>582613029.0044533</v>
@@ -948,88 +979,80 @@
         <v>1127180476.216861</v>
       </c>
       <c r="M12">
-        <v>669016160.9526911</v>
+        <v>669016160.95269108</v>
       </c>
       <c r="N12">
-        <v>1559847036.496355</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>1559847036.4963551</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
       </c>
       <c r="C13">
-        <v>20961.21919971283</v>
+        <v>20961.219199712828</v>
       </c>
       <c r="D13">
         <v>15514.44481423692</v>
       </c>
       <c r="E13">
-        <v>25469.59704319076</v>
+        <v>25469.597043190759</v>
       </c>
       <c r="F13">
         <v>3640.729485625794</v>
       </c>
       <c r="G13">
-        <v>2160.884538841149</v>
+        <v>2160.8845388411492</v>
       </c>
       <c r="H13">
-        <v>5038.218119159203</v>
+        <v>5038.2181191592026</v>
       </c>
       <c r="I13">
-        <v>352965970.1039641</v>
+        <v>352965970.10396409</v>
       </c>
       <c r="J13">
         <v>261247736.226935</v>
       </c>
       <c r="K13">
-        <v>428882544.6102901</v>
+        <v>428882544.61029011</v>
       </c>
       <c r="L13">
-        <v>484217021.5882306</v>
+        <v>484217021.58823061</v>
       </c>
       <c r="M13">
-        <v>287397643.6658728</v>
+        <v>287397643.66587281</v>
       </c>
       <c r="N13">
-        <v>670083009.848174</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>670083009.84817398</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>412256.2595949728</v>
+        <v>412256.25959497283</v>
       </c>
       <c r="D14">
-        <v>309599.5736041024</v>
+        <v>309599.57360410242</v>
       </c>
       <c r="E14">
-        <v>493594.8705806515</v>
+        <v>493594.87058065151</v>
       </c>
       <c r="F14">
-        <v>405272.4368740573</v>
+        <v>405272.43687405728</v>
       </c>
       <c r="G14">
-        <v>188273.2985055277</v>
+        <v>188273.29850552769</v>
       </c>
       <c r="H14">
-        <v>741469.7268240846</v>
+        <v>741469.72682408465</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1041,43 +1064,39 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>53901234104.24962</v>
+        <v>53901234104.249619</v>
       </c>
       <c r="M14">
-        <v>25040348701.23519</v>
+        <v>25040348701.235191</v>
       </c>
       <c r="N14">
-        <v>98615473667.60326</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>98615473667.603256</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>205076.2777874958</v>
+        <v>205076.27778749581</v>
       </c>
       <c r="D15">
-        <v>154009.8583868761</v>
+        <v>154009.85838687609</v>
       </c>
       <c r="E15">
         <v>245538.0517281426</v>
       </c>
       <c r="F15">
-        <v>171030.3668774941</v>
+        <v>171030.36687749409</v>
       </c>
       <c r="G15">
-        <v>79453.83990336121</v>
+        <v>79453.839903361208</v>
       </c>
       <c r="H15">
-        <v>312910.1016230398</v>
+        <v>312910.10162303981</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1089,13 +1108,13 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>22747038794.70671</v>
+        <v>22747038794.706711</v>
       </c>
       <c r="M15">
-        <v>10567360707.14704</v>
+        <v>10567360707.147039</v>
       </c>
       <c r="N15">
-        <v>41617043515.86429</v>
+        <v>41617043515.864288</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/cases_prev_7000steps.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0066AB-1925-6D42-B7C0-45CD847F934D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8AF402-E7C0-3F49-AE96-1BF12B9D93E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33380" yWindow="-780" windowWidth="24100" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>disease</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>Male</t>
-  </si>
-  <si>
-    <t>bc</t>
   </si>
   <si>
     <t>cvd</t>
@@ -441,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -518,13 +515,13 @@
         <v>68821.865817244281</v>
       </c>
       <c r="F2">
-        <v>118382.8271450311</v>
+        <v>710296.96287018666</v>
       </c>
       <c r="G2">
-        <v>101336.9266843623</v>
+        <v>608021.56010617362</v>
       </c>
       <c r="H2">
-        <v>133974.92653204821</v>
+        <v>803849.55919229076</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -536,13 +533,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>15744916010.289141</v>
+        <v>94469496061.734833</v>
       </c>
       <c r="M2">
-        <v>13477811249.020189</v>
+        <v>80866867494.121094</v>
       </c>
       <c r="N2">
-        <v>17818665228.762409</v>
+        <v>106911991372.57471</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
@@ -562,13 +559,13 @@
         <v>111372.7815803948</v>
       </c>
       <c r="F3">
-        <v>157474.83013748869</v>
+        <v>944848.98082493839</v>
       </c>
       <c r="G3">
-        <v>134800.0863058035</v>
+        <v>808800.51783481752</v>
       </c>
       <c r="H3">
-        <v>178215.70330019339</v>
+        <v>1069294.2198011631</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -580,13 +577,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>20944152408.285992</v>
+        <v>125664914449.7168</v>
       </c>
       <c r="M3">
-        <v>17928411478.671871</v>
+        <v>107570468872.0307</v>
       </c>
       <c r="N3">
-        <v>23702688538.92572</v>
+        <v>142216131233.55469</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -597,40 +594,40 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>5035.9010316036329</v>
+        <v>62026.800699346823</v>
       </c>
       <c r="D4">
-        <v>-105.13768319988129</v>
+        <v>40529.901885378029</v>
       </c>
       <c r="E4">
-        <v>10045.63284707618</v>
+        <v>81329.527380732266</v>
       </c>
       <c r="F4">
-        <v>1395.2524551587869</v>
+        <v>60473.368195140749</v>
       </c>
       <c r="G4">
-        <v>-21.907454231934391</v>
+        <v>31013.809380559051</v>
       </c>
       <c r="H4">
-        <v>3521.2879132382768</v>
+        <v>96656.993318942012</v>
       </c>
       <c r="I4">
-        <v>222017768.78030801</v>
+        <v>3455016852.5550218</v>
       </c>
       <c r="J4">
-        <v>-4635205.0392331639</v>
+        <v>2257596594.819324</v>
       </c>
       <c r="K4">
-        <v>442881815.32904661</v>
+        <v>4530217334.1615686</v>
       </c>
       <c r="L4">
-        <v>185568576.53611869</v>
+        <v>8042957969.9537191</v>
       </c>
       <c r="M4">
-        <v>-2913691.412847274</v>
+        <v>4124836647.6143532</v>
       </c>
       <c r="N4">
-        <v>468331292.46069092</v>
+        <v>12855380111.419291</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -641,40 +638,40 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>82750.82644288789</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>54071.511650600369</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>108502.8653595535</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>64825.831846597299</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>33245.973423191732</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>103613.709351729</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4609386534.5217505</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>3011891341.9617391</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>6043826606.2578449</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>8621835635.5974407</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>4421714465.2845001</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>13780623343.779961</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -685,40 +682,40 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>62026.800699346823</v>
+        <v>78495.714998487034</v>
       </c>
       <c r="D6">
-        <v>40529.901885378029</v>
+        <v>-1638.804568292139</v>
       </c>
       <c r="E6">
-        <v>81329.527380732266</v>
+        <v>156583.5245758266</v>
       </c>
       <c r="F6">
-        <v>10078.894699190099</v>
+        <v>139154.94733830521</v>
       </c>
       <c r="G6">
-        <v>5168.9682300931599</v>
+        <v>-2298.4918543887788</v>
       </c>
       <c r="H6">
-        <v>16109.498886490321</v>
+        <v>320532.08126525203</v>
       </c>
       <c r="I6">
-        <v>3455016852.5550218</v>
+        <v>1162286051.982595</v>
       </c>
       <c r="J6">
-        <v>2257596594.819324</v>
+        <v>-24265779.242701739</v>
       </c>
       <c r="K6">
-        <v>4530217334.1615686</v>
+        <v>2318532248.3942609</v>
       </c>
       <c r="L6">
-        <v>1340492994.9922831</v>
+        <v>18507607995.994598</v>
       </c>
       <c r="M6">
-        <v>687472774.60239029</v>
+        <v>-305699416.63370758</v>
       </c>
       <c r="N6">
-        <v>2142563351.9032121</v>
+        <v>42630766808.278519</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -729,40 +726,40 @@
         <v>16</v>
       </c>
       <c r="C7">
-        <v>82750.82644288789</v>
+        <v>49665.124841932273</v>
       </c>
       <c r="D7">
-        <v>54071.511650600369</v>
+        <v>-1036.890147154239</v>
       </c>
       <c r="E7">
-        <v>108502.8653595535</v>
+        <v>99072.163319973421</v>
       </c>
       <c r="F7">
-        <v>10804.30530776621</v>
+        <v>49809.890593158663</v>
       </c>
       <c r="G7">
-        <v>5540.9955705319708</v>
+        <v>-822.73487207059543</v>
       </c>
       <c r="H7">
-        <v>17268.951558621589</v>
+        <v>114733.0239046752</v>
       </c>
       <c r="I7">
-        <v>4609386534.5217505</v>
+        <v>735391503.53449142</v>
       </c>
       <c r="J7">
-        <v>3011891341.9617391</v>
+        <v>-15353232.40891281</v>
       </c>
       <c r="K7">
-        <v>6043826606.2578449</v>
+        <v>1466961522.2788451</v>
       </c>
       <c r="L7">
-        <v>1436972605.9329059</v>
+        <v>6624715448.8901024</v>
       </c>
       <c r="M7">
-        <v>736952410.88075209</v>
+        <v>-109423737.9853892</v>
       </c>
       <c r="N7">
-        <v>2296770557.2966719</v>
+        <v>15259492179.321791</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -773,40 +770,40 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>78495.714998487034</v>
+        <v>12056.6702807696</v>
       </c>
       <c r="D8">
-        <v>-1638.804568292139</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>156583.5245758266</v>
+        <v>21984.680831592039</v>
       </c>
       <c r="F8">
-        <v>23192.491223051009</v>
+        <v>25226.501047201051</v>
       </c>
       <c r="G8">
-        <v>-383.08197573146339</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>53422.013544208778</v>
+        <v>58401.25858151415</v>
       </c>
       <c r="I8">
-        <v>1162286051.982595</v>
+        <v>906673661.78415251</v>
       </c>
       <c r="J8">
-        <v>-24265779.242701739</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>2318532248.3942609</v>
+        <v>1653269983.216557</v>
       </c>
       <c r="L8">
-        <v>3084601332.6657839</v>
+        <v>3355124639.277739</v>
       </c>
       <c r="M8">
-        <v>-50949902.772284627</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>7105127801.3797674</v>
+        <v>7767367391.341382</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -817,40 +814,40 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>49665.124841932273</v>
+        <v>16096.82026023769</v>
       </c>
       <c r="D9">
-        <v>-1036.890147154239</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>99072.163319973421</v>
+        <v>29351.67401809747</v>
       </c>
       <c r="F9">
-        <v>8301.6484321931348</v>
+        <v>29628.576424769319</v>
       </c>
       <c r="G9">
-        <v>-137.12247867843229</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>19122.17065077916</v>
+        <v>68592.396145128412</v>
       </c>
       <c r="I9">
-        <v>735391503.53449142</v>
+        <v>1210496980.3901379</v>
       </c>
       <c r="J9">
-        <v>-15353232.40891281</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>1466961522.2788451</v>
+        <v>2207275237.8349309</v>
       </c>
       <c r="L9">
-        <v>1104119241.4816871</v>
+        <v>3940600664.494319</v>
       </c>
       <c r="M9">
-        <v>-18237289.664231502</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>2543248696.553628</v>
+        <v>9122788687.3020782</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -861,40 +858,40 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>12056.6702807696</v>
+        <v>28474.64780985158</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>21075.50843496856</v>
       </c>
       <c r="E10">
-        <v>21984.680831592039</v>
+        <v>34599.027792888832</v>
       </c>
       <c r="F10">
-        <v>4204.4168412001727</v>
+        <v>50850.247047377423</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>30181.18019335427</v>
       </c>
       <c r="H10">
-        <v>9733.5430969190547</v>
+        <v>70369.039240437065</v>
       </c>
       <c r="I10">
-        <v>906673661.78415251</v>
+        <v>479484594.47009218</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>354890486.53643668</v>
       </c>
       <c r="K10">
-        <v>1653269983.216557</v>
+        <v>582613029.0044533</v>
       </c>
       <c r="L10">
-        <v>559187439.87962294</v>
+        <v>6763082857.3011961</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>4014096965.7161169</v>
       </c>
       <c r="N10">
-        <v>1294561231.890234</v>
+        <v>9359082218.9781303</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -905,40 +902,40 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>16096.82026023769</v>
+        <v>20961.219199712828</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>15514.44481423692</v>
       </c>
       <c r="E11">
-        <v>29351.67401809747</v>
+        <v>25469.597043190759</v>
       </c>
       <c r="F11">
-        <v>4938.0960707948789</v>
+        <v>21844.37691375475</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>12965.307233046889</v>
       </c>
       <c r="H11">
-        <v>11432.066024188051</v>
+        <v>30229.308714955161</v>
       </c>
       <c r="I11">
-        <v>1210496980.3901379</v>
+        <v>352965970.10396409</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>261247736.226935</v>
       </c>
       <c r="K11">
-        <v>2207275237.8349309</v>
+        <v>428882544.61029011</v>
       </c>
       <c r="L11">
-        <v>656766777.41571891</v>
+        <v>2905302129.5293808</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1724385861.9952371</v>
       </c>
       <c r="N11">
-        <v>1520464781.217011</v>
+        <v>4020498059.089036</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -949,40 +946,40 @@
         <v>15</v>
       </c>
       <c r="C12">
-        <v>28474.64780985158</v>
+        <v>412256.25959497283</v>
       </c>
       <c r="D12">
-        <v>21075.50843496856</v>
+        <v>309599.57360410242</v>
       </c>
       <c r="E12">
-        <v>34599.027792888832</v>
+        <v>493594.87058065151</v>
       </c>
       <c r="F12">
-        <v>8475.0411745628644</v>
+        <v>1215817.310622175</v>
       </c>
       <c r="G12">
-        <v>5030.1966988924141</v>
+        <v>564819.89551658358</v>
       </c>
       <c r="H12">
-        <v>11728.17320673951</v>
+        <v>2224409.1804722599</v>
       </c>
       <c r="I12">
-        <v>479484594.47009218</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>354890486.53643668</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>582613029.0044533</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>1127180476.216861</v>
+        <v>161703702312.7493</v>
       </c>
       <c r="M12">
-        <v>669016160.95269108</v>
+        <v>75121046103.705612</v>
       </c>
       <c r="N12">
-        <v>1559847036.4963551</v>
+        <v>295846421002.81049</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -993,128 +990,40 @@
         <v>16</v>
       </c>
       <c r="C13">
-        <v>20961.219199712828</v>
+        <v>205076.27778749581</v>
       </c>
       <c r="D13">
-        <v>15514.44481423692</v>
+        <v>154009.85838687609</v>
       </c>
       <c r="E13">
-        <v>25469.597043190759</v>
+        <v>245538.0517281426</v>
       </c>
       <c r="F13">
-        <v>3640.729485625794</v>
+        <v>513091.10063248029</v>
       </c>
       <c r="G13">
-        <v>2160.8845388411492</v>
+        <v>238361.51971008419</v>
       </c>
       <c r="H13">
-        <v>5038.2181191592026</v>
+        <v>938730.30486912408</v>
       </c>
       <c r="I13">
-        <v>352965970.10396409</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>261247736.226935</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>428882544.61029011</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>484217021.58823061</v>
+        <v>68241116384.119888</v>
       </c>
       <c r="M13">
-        <v>287397643.66587281</v>
+        <v>31702082121.4412</v>
       </c>
       <c r="N13">
-        <v>670083009.84817398</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>412256.25959497283</v>
-      </c>
-      <c r="D14">
-        <v>309599.57360410242</v>
-      </c>
-      <c r="E14">
-        <v>493594.87058065151</v>
-      </c>
-      <c r="F14">
-        <v>405272.43687405728</v>
-      </c>
-      <c r="G14">
-        <v>188273.29850552769</v>
-      </c>
-      <c r="H14">
-        <v>741469.72682408465</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>53901234104.249619</v>
-      </c>
-      <c r="M14">
-        <v>25040348701.235191</v>
-      </c>
-      <c r="N14">
-        <v>98615473667.603256</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
-        <v>205076.27778749581</v>
-      </c>
-      <c r="D15">
-        <v>154009.85838687609</v>
-      </c>
-      <c r="E15">
-        <v>245538.0517281426</v>
-      </c>
-      <c r="F15">
-        <v>171030.36687749409</v>
-      </c>
-      <c r="G15">
-        <v>79453.839903361208</v>
-      </c>
-      <c r="H15">
-        <v>312910.10162303981</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>22747038794.706711</v>
-      </c>
-      <c r="M15">
-        <v>10567360707.147039</v>
-      </c>
-      <c r="N15">
-        <v>41617043515.864288</v>
+        <v>124851130547.59351</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/7000 steps/cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/cases_prev_7000steps.xlsx
@@ -8,14 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8AF402-E7C0-3F49-AE96-1BF12B9D93E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5773366C-F049-B849-8549-F742DF9B76B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/output/Tables/7000 steps/cases_prev_7000steps.xlsx
+++ b/output/Tables/7000 steps/cases_prev_7000steps.xlsx
@@ -1,110 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5773366C-F049-B849-8549-F742DF9B76B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>tot_cases_mid</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly_mid</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_mid</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_mid</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -204,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -238,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -273,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -449,91 +350,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_mid</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_mid</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C2">
-        <v>60812.327020701341</v>
+        <v>238857.6635929984</v>
       </c>
       <c r="D2">
-        <v>52055.982049259008</v>
+        <v>152710.3587038377</v>
       </c>
       <c r="E2">
-        <v>68821.865817244281</v>
+        <v>313164.55456395</v>
       </c>
       <c r="F2">
-        <v>710296.96287018666</v>
+        <v>2789892.795100919</v>
       </c>
       <c r="G2">
-        <v>608021.56010617362</v>
+        <v>1783679.54821443</v>
       </c>
       <c r="H2">
-        <v>803849.55919229076</v>
+        <v>3657808.258342886</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -545,39 +465,43 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>94469496061.734833</v>
+        <v>371055741748.4222</v>
       </c>
       <c r="M2">
-        <v>80866867494.121094</v>
+        <v>237229379912.5192</v>
       </c>
       <c r="N2">
-        <v>106911991372.57471</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+        <v>486488498359.6038</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C3">
-        <v>98411.136260928019</v>
+        <v>386537.6516641976</v>
       </c>
       <c r="D3">
-        <v>84240.95234675247</v>
+        <v>247127.5258672922</v>
       </c>
       <c r="E3">
-        <v>111372.7815803948</v>
+        <v>506786.7184361271</v>
       </c>
       <c r="F3">
-        <v>944848.98082493839</v>
+        <v>3711162.375536832</v>
       </c>
       <c r="G3">
-        <v>808800.51783481752</v>
+        <v>2372680.570727288</v>
       </c>
       <c r="H3">
-        <v>1069294.2198011631</v>
+        <v>4865678.139721884</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -589,391 +513,427 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>125664914449.7168</v>
+        <v>493584595946.3987</v>
       </c>
       <c r="M3">
-        <v>107570468872.0307</v>
+        <v>315566515906.7293</v>
       </c>
       <c r="N3">
-        <v>142216131233.55469</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
+        <v>647135192583.0106</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C4">
-        <v>62026.800699346823</v>
+        <v>1601497.101714449</v>
       </c>
       <c r="D4">
-        <v>40529.901885378029</v>
+        <v>1023895.123091814</v>
       </c>
       <c r="E4">
-        <v>81329.527380732266</v>
+        <v>2099711.262974003</v>
       </c>
       <c r="F4">
-        <v>60473.368195140749</v>
+        <v>2839088.029911194</v>
       </c>
       <c r="G4">
-        <v>31013.809380559051</v>
+        <v>1436055.674794394</v>
       </c>
       <c r="H4">
-        <v>96656.993318942012</v>
+        <v>4298184.135274271</v>
       </c>
       <c r="I4">
-        <v>3455016852.5550218</v>
+        <v>23713367585.0858</v>
       </c>
       <c r="J4">
-        <v>2257596594.819324</v>
+        <v>15160815087.62029</v>
       </c>
       <c r="K4">
-        <v>4530217334.1615686</v>
+        <v>31090424670.85612</v>
       </c>
       <c r="L4">
-        <v>8042957969.9537191</v>
+        <v>377598707978.1888</v>
       </c>
       <c r="M4">
-        <v>4124836647.6143532</v>
+        <v>190995404747.6544</v>
       </c>
       <c r="N4">
-        <v>12855380111.419291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
+        <v>571658489991.478</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C5">
-        <v>82750.82644288789</v>
+        <v>1013285.291970063</v>
       </c>
       <c r="D5">
-        <v>54071.511650600369</v>
+        <v>647830.0008399205</v>
       </c>
       <c r="E5">
-        <v>108502.8653595535</v>
+        <v>1328511.015023229</v>
       </c>
       <c r="F5">
-        <v>64825.831846597299</v>
+        <v>1016238.853588316</v>
       </c>
       <c r="G5">
-        <v>33245.973423191732</v>
+        <v>514029.7015333133</v>
       </c>
       <c r="H5">
-        <v>103613.709351729</v>
+        <v>1538515.774123152</v>
       </c>
       <c r="I5">
-        <v>4609386534.5217505</v>
+        <v>15003715318.20083</v>
       </c>
       <c r="J5">
-        <v>3011891341.9617391</v>
+        <v>9592418822.43663</v>
       </c>
       <c r="K5">
-        <v>6043826606.2578449</v>
+        <v>19671262599.44902</v>
       </c>
       <c r="L5">
-        <v>8621835635.5974407</v>
+        <v>135159767527.246</v>
       </c>
       <c r="M5">
-        <v>4421714465.2845001</v>
+        <v>68365950303.93067</v>
       </c>
       <c r="N5">
-        <v>13780623343.779961</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
+        <v>204622597958.3792</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C6">
-        <v>78495.714998487034</v>
+        <v>377828.9153114689</v>
       </c>
       <c r="D6">
-        <v>-1638.804568292139</v>
+        <v>241559.7151792117</v>
       </c>
       <c r="E6">
-        <v>156583.5245758266</v>
+        <v>495368.7572131407</v>
       </c>
       <c r="F6">
-        <v>139154.94733830521</v>
+        <v>368366.3650677601</v>
       </c>
       <c r="G6">
-        <v>-2298.4918543887788</v>
+        <v>184843.4516761787</v>
       </c>
       <c r="H6">
-        <v>320532.08126525203</v>
+        <v>588726.5818257635</v>
       </c>
       <c r="I6">
-        <v>1162286051.982595</v>
+        <v>21045826240.67933</v>
       </c>
       <c r="J6">
-        <v>-24265779.242701739</v>
+        <v>13455359254.91232</v>
       </c>
       <c r="K6">
-        <v>2318532248.3942609</v>
+        <v>27593030514.28617</v>
       </c>
       <c r="L6">
-        <v>18507607995.994598</v>
+        <v>48992726554.01208</v>
       </c>
       <c r="M6">
-        <v>-305699416.63370758</v>
+        <v>24584179072.93177</v>
       </c>
       <c r="N6">
-        <v>42630766808.278519</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
+        <v>78300635382.82654</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C7">
-        <v>49665.124841932273</v>
+        <v>504066.8653473335</v>
       </c>
       <c r="D7">
-        <v>-1036.890147154239</v>
+        <v>322268.2105317547</v>
       </c>
       <c r="E7">
-        <v>99072.163319973421</v>
+        <v>660878.4201537042</v>
       </c>
       <c r="F7">
-        <v>49809.890593158663</v>
+        <v>394878.8822671145</v>
       </c>
       <c r="G7">
-        <v>-822.73487207059543</v>
+        <v>198147.2319788455</v>
       </c>
       <c r="H7">
-        <v>114733.0239046752</v>
+        <v>631099.1356377783</v>
       </c>
       <c r="I7">
-        <v>735391503.53449142</v>
+        <v>28077532533.5774</v>
       </c>
       <c r="J7">
-        <v>-15353232.40891281</v>
+        <v>17950983863.03995</v>
       </c>
       <c r="K7">
-        <v>1466961522.2788451</v>
+        <v>36812249759.40205</v>
       </c>
       <c r="L7">
-        <v>6624715448.8901024</v>
+        <v>52518891341.52622</v>
       </c>
       <c r="M7">
-        <v>-109423737.9853892</v>
+        <v>26353581853.18645</v>
       </c>
       <c r="N7">
-        <v>15259492179.321791</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>83936185039.82452</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C8">
-        <v>12056.6702807696</v>
+        <v>110697.7559144882</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>70773.08619335832</v>
       </c>
       <c r="E8">
-        <v>21984.680831592039</v>
+        <v>145135.0268637823</v>
       </c>
       <c r="F8">
-        <v>25226.501047201051</v>
+        <v>231615.9429153254</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>110199.9339510133</v>
       </c>
       <c r="H8">
-        <v>58401.25858151415</v>
+        <v>385544.2932301505</v>
       </c>
       <c r="I8">
-        <v>906673661.78415251</v>
+        <v>8324581942.525422</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>5322206854.826803</v>
       </c>
       <c r="K8">
-        <v>1653269983.216557</v>
+        <v>10914299155.18317</v>
       </c>
       <c r="L8">
-        <v>3355124639.277739</v>
+        <v>30804920407.73828</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>14656591215.48477</v>
       </c>
       <c r="N8">
-        <v>7767367391.341382</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
+        <v>51277390999.61002</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C9">
-        <v>16096.82026023769</v>
+        <v>147792.2045367108</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>94488.91121571569</v>
       </c>
       <c r="E9">
-        <v>29351.67401809747</v>
+        <v>193769.2900681982</v>
       </c>
       <c r="F9">
-        <v>29628.576424769319</v>
+        <v>272033.3927016482</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>129430.0449738508</v>
       </c>
       <c r="H9">
-        <v>68592.396145128412</v>
+        <v>452822.5510041864</v>
       </c>
       <c r="I9">
-        <v>1210496980.3901379</v>
+        <v>11114121573.36506</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>7105660612.333069</v>
       </c>
       <c r="K9">
-        <v>2207275237.8349309</v>
+        <v>14571644382.41854</v>
       </c>
       <c r="L9">
-        <v>3940600664.494319</v>
+        <v>36180441229.31921</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>17214195981.52216</v>
       </c>
       <c r="N9">
-        <v>9122788687.3020782</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
+        <v>60225399283.5568</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C10">
-        <v>28474.64780985158</v>
+        <v>112326.0658534857</v>
       </c>
       <c r="D10">
-        <v>21075.50843496856</v>
+        <v>71814.12373481671</v>
       </c>
       <c r="E10">
-        <v>34599.027792888832</v>
+        <v>147269.8922437222</v>
       </c>
       <c r="F10">
-        <v>50850.247047377423</v>
+        <v>200592.7601511383</v>
       </c>
       <c r="G10">
-        <v>30181.18019335427</v>
+        <v>102841.410234836</v>
       </c>
       <c r="H10">
-        <v>70369.039240437065</v>
+        <v>299524.0469838683</v>
       </c>
       <c r="I10">
-        <v>479484594.47009218</v>
+        <v>1891458622.90685</v>
       </c>
       <c r="J10">
-        <v>354890486.53643668</v>
+        <v>1209278029.570587</v>
       </c>
       <c r="K10">
-        <v>582613029.0044533</v>
+        <v>2479877715.492043</v>
       </c>
       <c r="L10">
-        <v>6763082857.3011961</v>
+        <v>26678837100.1014</v>
       </c>
       <c r="M10">
-        <v>4014096965.7161169</v>
+        <v>13677907561.23319</v>
       </c>
       <c r="N10">
-        <v>9359082218.9781303</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
+        <v>39836698248.85449</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C11">
-        <v>20961.219199712828</v>
+        <v>82687.28392776458</v>
       </c>
       <c r="D11">
-        <v>15514.44481423692</v>
+        <v>52864.97656768151</v>
       </c>
       <c r="E11">
-        <v>25469.597043190759</v>
+        <v>108410.6997021651</v>
       </c>
       <c r="F11">
-        <v>21844.37691375475</v>
+        <v>86171.141997193</v>
       </c>
       <c r="G11">
-        <v>12965.307233046889</v>
+        <v>44178.87145009841</v>
       </c>
       <c r="H11">
-        <v>30229.308714955161</v>
+        <v>128670.2928100386</v>
       </c>
       <c r="I11">
-        <v>352965970.10396409</v>
+        <v>1392371174.059618</v>
       </c>
       <c r="J11">
-        <v>261247736.226935</v>
+        <v>890193340.4231979</v>
       </c>
       <c r="K11">
-        <v>428882544.61029011</v>
+        <v>1825527772.28476</v>
       </c>
       <c r="L11">
-        <v>2905302129.5293808</v>
+        <v>11460761885.62667</v>
       </c>
       <c r="M11">
-        <v>1724385861.9952371</v>
+        <v>5875789902.863089</v>
       </c>
       <c r="N11">
-        <v>4020498059.089036</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
+        <v>17113148943.73514</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
       </c>
       <c r="C12">
-        <v>412256.25959497283</v>
+        <v>2427778.301906202</v>
       </c>
       <c r="D12">
-        <v>309599.57360410242</v>
+        <v>1552166.632464546</v>
       </c>
       <c r="E12">
-        <v>493594.87058065151</v>
+        <v>3183042.566270728</v>
       </c>
       <c r="F12">
-        <v>1215817.310622175</v>
+        <v>7159951.649273743</v>
       </c>
       <c r="G12">
-        <v>564819.89551658358</v>
+        <v>2831704.788760517</v>
       </c>
       <c r="H12">
-        <v>2224409.1804722599</v>
+        <v>14344535.42419801</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -985,39 +945,43 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>161703702312.7493</v>
+        <v>952273569353.4078</v>
       </c>
       <c r="M12">
-        <v>75121046103.705612</v>
+        <v>376616736905.1488</v>
       </c>
       <c r="N12">
-        <v>295846421002.81049</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
+        <v>1907823211418.336</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
       <c r="C13">
-        <v>205076.27778749581</v>
+        <v>1207694.791432209</v>
       </c>
       <c r="D13">
-        <v>154009.85838687609</v>
+        <v>772123.0377545063</v>
       </c>
       <c r="E13">
-        <v>245538.0517281426</v>
+        <v>1583399.903184671</v>
       </c>
       <c r="F13">
-        <v>513091.10063248029</v>
+        <v>3021594.97163374</v>
       </c>
       <c r="G13">
-        <v>238361.51971008419</v>
+        <v>1195017.141175513</v>
       </c>
       <c r="H13">
-        <v>938730.30486912408</v>
+        <v>6053585.028409338</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1029,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>68241116384.119888</v>
+        <v>401872131227.2874</v>
       </c>
       <c r="M13">
-        <v>31702082121.4412</v>
+        <v>158937279776.3433</v>
       </c>
       <c r="N13">
-        <v>124851130547.59351</v>
+        <v>805126808778.4419</v>
       </c>
     </row>
   </sheetData>
